--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3036" yWindow="2340" windowWidth="11268" windowHeight="9900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1071,6 +1071,366 @@
         </is>
       </c>
     </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>9:16:27 AM</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>10:10:16 AM</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00001</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>VX156080:ABA51202605281A00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>10:10:33 AM</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00002</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>VX156070:ABA51202605281A00002</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>10:12:14 AM</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00003</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>10:12:33 AM</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00004</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>VX155800:ABA51202605281A00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>12:51:14 PM</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00001</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>VX156080:ABA51202605281A00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>1:03:22 PM</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00001</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>VX156080:ABA51202605281A00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>1:03:57 PM</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00002</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>VX156070:ABA51202605281A00002</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>1:04:09 PM</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00003</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>1:04:21 PM</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00004</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>VX155800:ABA51202605281A00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>1:07:38 PM</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00003</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00003</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>21 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>1:49:02 PM</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609211A00009</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202609211A00009</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1431,276 @@
         </is>
       </c>
     </row>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>3:26:58 PM</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202605281A00119</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202605281A00119</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>3:28:10 PM</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202605281A00119</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202605281A00119</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>3:28:48 PM</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609281A00200</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609281A00200</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>10 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>3:29:01 PM</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609101A00076</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609101A00076</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>3:29:11 PM</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202605281A00114</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202605281A00114</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>3:31:21 PM</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202605281A00119</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>VX156080:ABA31202605281A00119</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>3:31:38 PM</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609281A00200</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>VX156070:ABA41202609281A00200</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>10 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>3:31:50 PM</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609101A00076</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202609101A00076</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>3:32:02 PM</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202605281A00114</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>VX155800:ABA61202605281A00114</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1701,6 +1701,36 @@
         </is>
       </c>
     </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>3:29:39 PM</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A123456</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A123456</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1731,6 +1731,336 @@
         </is>
       </c>
     </row>
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>3:41:08 PM</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202608231A00289</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202608231A00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>3:43:01 PM</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202608231A00289</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202608231A00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>3:44:42 PM</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202608231A00289</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202608231A00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>3:45:00 PM</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609251A00296</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609251A00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>3:45:13 PM</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609251A00298</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609251A00298</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>3:45:26 PM</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202609241A00291</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609241A00291</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>5:17:38 PM</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202608231A00289</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202608231A00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>7:15:33 PM</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>7:57:34 PM</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609251A00296</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609251A00296</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>23 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>7:58:01 PM</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202608231A00289</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202608231A00289</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>7:58:29 PM</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2061,6 +2061,96 @@
         </is>
       </c>
     </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>11:03:03 AM</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>11:03:57 AM</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="18" customHeight="1">
+      <c r="A56" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>11:10:00 AM</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2151,36 @@
         </is>
       </c>
     </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>3:26:18 PM</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2181,66 @@
         </is>
       </c>
     </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>11:10:11 AM</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00111</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>11:52:58 AM</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281A00112</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281A00112</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2151,6 +2151,366 @@
         </is>
       </c>
     </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>3:49:24 PM</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202610121U00001</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202610121U00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>3:49:33 PM</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202610121A00001</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202610121A00001</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="18" customHeight="1">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>4:04:29 PM</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="18" customHeight="1">
+      <c r="A60" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>4:04:32 PM</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="18" customHeight="1">
+      <c r="A61" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>4:04:33 PM</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="18" customHeight="1">
+      <c r="A62" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>4:04:34 PM</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>4:04:35 PM</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>4:04:35 PM</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>4:04:37 PM</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>4:04:38 PM</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>4:04:40 PM</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="18" customHeight="1">
+      <c r="A68" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>4:04:41 PM</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2511,6 +2511,36 @@
         </is>
       </c>
     </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>3:58:11 PM</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2541,6 +2541,396 @@
         </is>
       </c>
     </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>4:30:39 PM</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>4:32:42 PM</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>4:32:58 PM</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>4:33:15 PM</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>4:33:17 PM</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>4:33:19 PM</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>4:33:21 PM</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>4:33:22 PM</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>4:33:26 PM</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>4:33:28 PM</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>4:33:40 PM</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>4:33:52 PM</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>4:33:57 PM</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U12345</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U12345</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2541,6 +2541,66 @@
         </is>
       </c>
     </row>
+    <row r="70" ht="18" customHeight="1">
+      <c r="A70" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>9:58:22 AM</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>10:07:11 AM</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3036" yWindow="2340" windowWidth="11268" windowHeight="9900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2601,6 +2601,126 @@
         </is>
       </c>
     </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>4:40:49 PM</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>4:58:42 PM</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="18" customHeight="1">
+      <c r="A74" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>8:35:47 AM</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>11:29:15 AM</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2721,6 +2721,66 @@
         </is>
       </c>
     </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>2:33:05 PM</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00111</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00111</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="18" customHeight="1">
+      <c r="A77" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>2:33:16 PM</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00112</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00112</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2781,6 +2781,426 @@
         </is>
       </c>
     </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>04:27:47 PM</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>04:46:45 PM</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00106</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00106</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="18" customHeight="1">
+      <c r="A80" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>04:46:48 PM</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00104</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00104</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>04:46:55 PM</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00104</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00104</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="6" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>04:47:01 PM</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00103</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00103</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="18" customHeight="1">
+      <c r="A83" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>04:48:23 PM</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="6" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>04:49:39 PM</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00100</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00100</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>04:59:12 PM</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="6" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>04:59:16 PM</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00104</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00104</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="18" customHeight="1">
+      <c r="A87" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>04:59:21 PM</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00103</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00103</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="6" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>04:59:25 PM</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00102</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00102</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>05:00:32 PM</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>05:00:37 PM</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>05:00:41 PM</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00109</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00109</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3036" yWindow="2340" windowWidth="11268" windowHeight="9900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3201,6 +3201,246 @@
         </is>
       </c>
     </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="6" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>09:53:56 AM</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>09:53:59 AM</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00105</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00105</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="6" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>09:54:02 AM</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00109</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00109</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>09:54:09 AM</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00101</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F95" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00101</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>09:55:51 AM</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>09:56:51 AM</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00100</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00100</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>11:23:59 AM</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00108</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00108</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>11:53:23 AM</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00101</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3441,6 +3441,486 @@
         </is>
       </c>
     </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="6" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>12:39:25 PM</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00106</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00106</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>12:42:42 PM</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00106</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00106</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="6" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>12:43:40 PM</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00106</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00106</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>12:49:32 PM</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00118</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00118</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="6" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>01:03:04 PM</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00118</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00118</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>01:06:45 PM</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00118</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00118</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="6" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>02:05:23 PM</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00118</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00118</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>04:47:08 PM</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00118</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00118</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="18" customHeight="1">
+      <c r="A108" s="6" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>04:49:04 PM</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00118</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00118</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="18" customHeight="1">
+      <c r="A109" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>04:49:11 PM</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00119</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00119</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="18" customHeight="1">
+      <c r="A110" s="6" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>08:44:54 AM</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00118</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00118</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="18" customHeight="1">
+      <c r="A111" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>08:47:00 AM</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00119</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00119</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="18" customHeight="1">
+      <c r="A112" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>09:14:35 AM</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00123</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00123</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="18" customHeight="1">
+      <c r="A113" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>09:17:38 AM</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00127</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00127</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="18" customHeight="1">
+      <c r="A114" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>09:23:55 AM</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00124</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00124</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="18" customHeight="1">
+      <c r="A115" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>10:29:24 AM</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00125</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00125</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -3921,6 +3921,66 @@
         </is>
       </c>
     </row>
+    <row r="116" ht="18" customHeight="1">
+      <c r="A116" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>11:39:20 AM</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="18" customHeight="1">
+      <c r="A117" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>11:41:14 AM</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,14 @@
       <name val="Segoe UI"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +63,11 @@
         <fgColor rgb="00EEF2F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,6 +103,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,8 +472,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:H119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
@@ -467,9 +481,11 @@
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28.05" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sl.No</t>
@@ -498,6 +514,16 @@
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Pack QR Data</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>Machine Name</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>Machine ID</t>
         </is>
       </c>
     </row>
@@ -3978,6 +4004,86 @@
       <c r="F117" s="5" t="inlineStr">
         <is>
           <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="18" customHeight="1">
+      <c r="A118" s="6" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>12:44:10 PM</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>bat_pc</t>
+        </is>
+      </c>
+      <c r="H118" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="18" customHeight="1">
+      <c r="A119" s="4" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>12:45:53 PM</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>bat_pc</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H119"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4087,6 +4087,86 @@
         </is>
       </c>
     </row>
+    <row r="120" ht="18" customHeight="1">
+      <c r="A120" s="6" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>01:36:56 PM</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00135</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00135</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>pc_2</t>
+        </is>
+      </c>
+      <c r="H120" s="6" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="18" customHeight="1">
+      <c r="A121" s="4" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>01:56:14 PM</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4167,6 +4167,1038 @@
         </is>
       </c>
     </row>
+    <row r="122" ht="18" customHeight="1">
+      <c r="A122" s="6" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>03:03:29 PM</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>machine 1</t>
+        </is>
+      </c>
+      <c r="H122" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="18" customHeight="1">
+      <c r="A123" s="4" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>03:03:36 PM</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00136</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00136</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>machine 1</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="18" customHeight="1">
+      <c r="A124" s="6" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>03:04:23 PM</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>machine 1</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="18" customHeight="1">
+      <c r="A125" s="4" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>03:04:29 PM</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>machine 1</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="18" customHeight="1">
+      <c r="A126" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>03:05:17 PM</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>machine 1</t>
+        </is>
+      </c>
+      <c r="H126" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="18" customHeight="1">
+      <c r="A127" s="4" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>03:05:22 PM</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>machine 1</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="18" customHeight="1">
+      <c r="A128" s="6" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>03:49:51 PM</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>VX156080:ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>PC_3</t>
+        </is>
+      </c>
+      <c r="H128" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="18" customHeight="1">
+      <c r="A129" s="4" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>04:02:05 PM</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>VX156080:ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="18" customHeight="1">
+      <c r="A130" s="6" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>04:05:01 PM</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>VX156080:ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="18" customHeight="1">
+      <c r="A131" s="4" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>04:13:52 PM</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610231U00137</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>VX156080:ABA31202610231U00137</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="18" customHeight="1">
+      <c r="A132" s="6" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>04:16:58 PM</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202610231R00138</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202610231R00138</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="18" customHeight="1">
+      <c r="A133" s="4" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>04:17:07 PM</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00139</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00139</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="18" customHeight="1">
+      <c r="A134" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>04:17:18 PM</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610231R00140</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610231R00140</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="18" customHeight="1">
+      <c r="A135" s="4" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>04:21:47 PM</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610231U00137</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>VX156080:ABA31202610231U00137</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="inlineStr"/>
+    </row>
+    <row r="136" ht="18" customHeight="1">
+      <c r="A136" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>04:22:02 PM</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202610231R00138</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202610231R00138</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137" ht="18" customHeight="1">
+      <c r="A137" s="4" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>04:22:12 PM</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00139</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00139</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="4" t="inlineStr"/>
+    </row>
+    <row r="138" ht="18" customHeight="1">
+      <c r="A138" s="6" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>04:22:20 PM</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610231R00140</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610231R00140</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139" ht="18" customHeight="1">
+      <c r="A139" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>04:50:21 PM</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610231R00137</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr"/>
+      <c r="H139" s="4" t="inlineStr"/>
+    </row>
+    <row r="140" ht="18" customHeight="1">
+      <c r="A140" s="6" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>04:50:31 PM</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202610231R00138</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202610231R00138</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="6" t="inlineStr"/>
+    </row>
+    <row r="141" ht="18" customHeight="1">
+      <c r="A141" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>04:50:41 PM</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281R00139</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202605281R00139</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr"/>
+      <c r="H141" s="4" t="inlineStr"/>
+    </row>
+    <row r="142" ht="18" customHeight="1">
+      <c r="A142" s="6" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>04:50:49 PM</t>
+        </is>
+      </c>
+      <c r="D142" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610231R00140</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610231R00140</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="inlineStr"/>
+    </row>
+    <row r="143" ht="18" customHeight="1">
+      <c r="A143" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>05:02:44 PM</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr"/>
+      <c r="H143" s="4" t="inlineStr"/>
+    </row>
+    <row r="144" ht="18" customHeight="1">
+      <c r="A144" s="6" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>05:02:53 PM</t>
+        </is>
+      </c>
+      <c r="D144" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610121R00330</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F144" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610121R00330</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="inlineStr"/>
+    </row>
+    <row r="145" ht="18" customHeight="1">
+      <c r="A145" s="4" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>05:03:02 PM</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00277</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F145" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00277</t>
+        </is>
+      </c>
+      <c r="G145" s="4" t="inlineStr"/>
+      <c r="H145" s="4" t="inlineStr"/>
+    </row>
+    <row r="146" ht="18" customHeight="1">
+      <c r="A146" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>05:03:12 PM</t>
+        </is>
+      </c>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609261R00299</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609261R00299</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147" ht="18" customHeight="1">
+      <c r="A147" s="4" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>05:03:21 PM</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="E147" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F147" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="G147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr"/>
+    </row>
+    <row r="148" ht="18" customHeight="1">
+      <c r="A148" s="6" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>05:03:58 PM</t>
+        </is>
+      </c>
+      <c r="D148" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149" ht="18" customHeight="1">
+      <c r="A149" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>08:29:09 AM</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F149" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="inlineStr"/>
+      <c r="H149" s="4" t="inlineStr"/>
+    </row>
+    <row r="150" ht="18" customHeight="1">
+      <c r="A150" s="6" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>08:45:41 AM</t>
+        </is>
+      </c>
+      <c r="D150" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F150" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5199,6 +5199,142 @@
       <c r="G150" s="6" t="inlineStr"/>
       <c r="H150" s="6" t="inlineStr"/>
     </row>
+    <row r="151" ht="18" customHeight="1">
+      <c r="A151" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>10:31:47 AM</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F151" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="18" customHeight="1">
+      <c r="A152" s="6" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>10:52:03 AM</t>
+        </is>
+      </c>
+      <c r="D152" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F152" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="6" t="inlineStr"/>
+    </row>
+    <row r="153" ht="18" customHeight="1">
+      <c r="A153" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>02:33:31 PM</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="G153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr"/>
+    </row>
+    <row r="154" ht="18" customHeight="1">
+      <c r="A154" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>02:34:12 PM</t>
+        </is>
+      </c>
+      <c r="D154" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F154" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5335,6 +5335,198 @@
       <c r="G154" s="6" t="inlineStr"/>
       <c r="H154" s="6" t="inlineStr"/>
     </row>
+    <row r="155" ht="18" customHeight="1">
+      <c r="A155" s="4" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>04:19:00 PM</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F155" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="G155" s="4" t="inlineStr"/>
+      <c r="H155" s="4" t="inlineStr"/>
+    </row>
+    <row r="156" ht="18" customHeight="1">
+      <c r="A156" s="6" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>04:33:10 PM</t>
+        </is>
+      </c>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F156" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="6" t="inlineStr"/>
+    </row>
+    <row r="157" ht="18" customHeight="1">
+      <c r="A157" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>04:33:18 PM</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F157" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="inlineStr"/>
+      <c r="H157" s="4" t="inlineStr"/>
+    </row>
+    <row r="158" ht="18" customHeight="1">
+      <c r="A158" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>04:36:20 PM</t>
+        </is>
+      </c>
+      <c r="D158" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F158" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr"/>
+    </row>
+    <row r="159" ht="18" customHeight="1">
+      <c r="A159" s="4" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>04:45:32 PM</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="E159" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F159" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="G159" s="4" t="inlineStr"/>
+      <c r="H159" s="4" t="inlineStr"/>
+    </row>
+    <row r="160" ht="18" customHeight="1">
+      <c r="A160" s="6" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>04:53:05 PM</t>
+        </is>
+      </c>
+      <c r="D160" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F160" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609242R00295</t>
+        </is>
+      </c>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5527,6 +5527,390 @@
       <c r="G160" s="6" t="inlineStr"/>
       <c r="H160" s="6" t="inlineStr"/>
     </row>
+    <row r="161" ht="18" customHeight="1">
+      <c r="A161" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>09:33:42 AM</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="E161" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00134</t>
+        </is>
+      </c>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="18" customHeight="1">
+      <c r="A162" s="6" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>09:36:03 AM</t>
+        </is>
+      </c>
+      <c r="D162" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F162" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="G162" s="6" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H162" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="18" customHeight="1">
+      <c r="A163" s="4" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>09:55:24 AM</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="18" customHeight="1">
+      <c r="A164" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>28 May 2026</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>09:59:07 AM</t>
+        </is>
+      </c>
+      <c r="D164" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202605281U00137</t>
+        </is>
+      </c>
+      <c r="G164" s="6" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H164" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="18" customHeight="1">
+      <c r="A165" s="4" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>11:15:41 AM</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="E165" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="G165" s="4" t="inlineStr"/>
+      <c r="H165" s="4" t="inlineStr"/>
+    </row>
+    <row r="166" ht="18" customHeight="1">
+      <c r="A166" s="6" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>11:26:04 AM</t>
+        </is>
+      </c>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr"/>
+      <c r="H166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167" ht="18" customHeight="1">
+      <c r="A167" s="4" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>11:26:24 AM</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="G167" s="4" t="inlineStr"/>
+      <c r="H167" s="4" t="inlineStr"/>
+    </row>
+    <row r="168" ht="18" customHeight="1">
+      <c r="A168" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>11:26:35 AM</t>
+        </is>
+      </c>
+      <c r="D168" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609261R00299</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F168" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609261R00299</t>
+        </is>
+      </c>
+      <c r="G168" s="6" t="inlineStr"/>
+      <c r="H168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169" ht="18" customHeight="1">
+      <c r="A169" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>11:26:45 AM</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00277</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00277</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr"/>
+      <c r="H169" s="4" t="inlineStr"/>
+    </row>
+    <row r="170" ht="18" customHeight="1">
+      <c r="A170" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>11:26:53 AM</t>
+        </is>
+      </c>
+      <c r="D170" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610121R00330</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F170" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610121R00330</t>
+        </is>
+      </c>
+      <c r="G170" s="6" t="inlineStr"/>
+      <c r="H170" s="6" t="inlineStr"/>
+    </row>
+    <row r="171" ht="18" customHeight="1">
+      <c r="A171" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>11:27:04 AM</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="G171" s="4" t="inlineStr"/>
+      <c r="H171" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H171"/>
+  <dimension ref="A1:H226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5911,6 +5911,1766 @@
       <c r="G171" s="4" t="inlineStr"/>
       <c r="H171" s="4" t="inlineStr"/>
     </row>
+    <row r="172" ht="18" customHeight="1">
+      <c r="A172" s="6" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>16 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>12:43:06 PM</t>
+        </is>
+      </c>
+      <c r="D172" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609161R00278</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609161R00278</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr"/>
+      <c r="H172" s="6" t="inlineStr"/>
+    </row>
+    <row r="173" ht="18" customHeight="1">
+      <c r="A173" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>16 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>12:44:11 PM</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609161R00278</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F173" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609161R00278</t>
+        </is>
+      </c>
+      <c r="G173" s="4" t="inlineStr"/>
+      <c r="H173" s="4" t="inlineStr"/>
+    </row>
+    <row r="174" ht="18" customHeight="1">
+      <c r="A174" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>08 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>12:44:28 PM</t>
+        </is>
+      </c>
+      <c r="D174" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609081R00280</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609081R00280</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr"/>
+      <c r="H174" s="6" t="inlineStr"/>
+    </row>
+    <row r="175" ht="18" customHeight="1">
+      <c r="A175" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>12:44:52 PM</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609181R00281</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F175" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609181R00281</t>
+        </is>
+      </c>
+      <c r="G175" s="4" t="inlineStr"/>
+      <c r="H175" s="4" t="inlineStr"/>
+    </row>
+    <row r="176" ht="18" customHeight="1">
+      <c r="A176" s="6" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>12:45:04 PM</t>
+        </is>
+      </c>
+      <c r="D176" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202609181R00282</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F176" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609181R00282</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr"/>
+      <c r="H176" s="6" t="inlineStr"/>
+    </row>
+    <row r="177" ht="18" customHeight="1">
+      <c r="A177" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>12:45:14 PM</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609191R00283</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F177" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609191R00283</t>
+        </is>
+      </c>
+      <c r="G177" s="4" t="inlineStr"/>
+      <c r="H177" s="4" t="inlineStr"/>
+    </row>
+    <row r="178" ht="18" customHeight="1">
+      <c r="A178" s="6" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>12:45:25 PM</t>
+        </is>
+      </c>
+      <c r="D178" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609191R00284</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609191R00284</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr"/>
+      <c r="H178" s="6" t="inlineStr"/>
+    </row>
+    <row r="179" ht="18" customHeight="1">
+      <c r="A179" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>12:45:37 PM</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609191R00286</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F179" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609191R00286</t>
+        </is>
+      </c>
+      <c r="G179" s="4" t="inlineStr"/>
+      <c r="H179" s="4" t="inlineStr"/>
+    </row>
+    <row r="180" ht="18" customHeight="1">
+      <c r="A180" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="6" t="inlineStr">
+        <is>
+          <t>22 Aug 2026</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>12:45:58 PM</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202608221R00288</t>
+        </is>
+      </c>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202608221R00288</t>
+        </is>
+      </c>
+      <c r="G180" s="6" t="inlineStr"/>
+      <c r="H180" s="6" t="inlineStr"/>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>12:46:12 PM</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="G181" s="4" t="inlineStr"/>
+      <c r="H181" s="4" t="inlineStr"/>
+    </row>
+    <row r="182" ht="18" customHeight="1">
+      <c r="A182" s="6" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="6" t="inlineStr">
+        <is>
+          <t>25 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>12:46:23 PM</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="E182" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609251R00297</t>
+        </is>
+      </c>
+      <c r="G182" s="6" t="inlineStr"/>
+      <c r="H182" s="6" t="inlineStr"/>
+    </row>
+    <row r="183" ht="18" customHeight="1">
+      <c r="A183" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>12:46:49 PM</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609261R00299</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F183" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609261R00299</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr"/>
+      <c r="H183" s="4" t="inlineStr"/>
+    </row>
+    <row r="184" ht="18" customHeight="1">
+      <c r="A184" s="6" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>12:46:56 PM</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609261R00300</t>
+        </is>
+      </c>
+      <c r="E184" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609261R00300</t>
+        </is>
+      </c>
+      <c r="G184" s="6" t="inlineStr"/>
+      <c r="H184" s="6" t="inlineStr"/>
+    </row>
+    <row r="185" ht="18" customHeight="1">
+      <c r="A185" s="4" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>12:47:07 PM</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609261R00301</t>
+        </is>
+      </c>
+      <c r="E185" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F185" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609261R00301</t>
+        </is>
+      </c>
+      <c r="G185" s="4" t="inlineStr"/>
+      <c r="H185" s="4" t="inlineStr"/>
+    </row>
+    <row r="186" ht="18" customHeight="1">
+      <c r="A186" s="6" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="6" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>12:47:15 PM</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609261R00302</t>
+        </is>
+      </c>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609261R00302</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="inlineStr"/>
+      <c r="H186" s="6" t="inlineStr"/>
+    </row>
+    <row r="187" ht="18" customHeight="1">
+      <c r="A187" s="4" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>12:47:24 PM</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609261R00303</t>
+        </is>
+      </c>
+      <c r="E187" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F187" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609261R00303</t>
+        </is>
+      </c>
+      <c r="G187" s="4" t="inlineStr"/>
+      <c r="H187" s="4" t="inlineStr"/>
+    </row>
+    <row r="188" ht="18" customHeight="1">
+      <c r="A188" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>12:47:33 PM</t>
+        </is>
+      </c>
+      <c r="D188" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609261R00304</t>
+        </is>
+      </c>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609261R00304</t>
+        </is>
+      </c>
+      <c r="G188" s="6" t="inlineStr"/>
+      <c r="H188" s="6" t="inlineStr"/>
+    </row>
+    <row r="189" ht="18" customHeight="1">
+      <c r="A189" s="4" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>26 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>12:47:41 PM</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609261R00305</t>
+        </is>
+      </c>
+      <c r="E189" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F189" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609261R00305</t>
+        </is>
+      </c>
+      <c r="G189" s="4" t="inlineStr"/>
+      <c r="H189" s="4" t="inlineStr"/>
+    </row>
+    <row r="190" ht="18" customHeight="1">
+      <c r="A190" s="6" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="6" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>12:48:05 PM</t>
+        </is>
+      </c>
+      <c r="D190" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609281R00306</t>
+        </is>
+      </c>
+      <c r="E190" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609281R00306</t>
+        </is>
+      </c>
+      <c r="G190" s="6" t="inlineStr"/>
+      <c r="H190" s="6" t="inlineStr"/>
+    </row>
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>12:48:15 PM</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609291R00307</t>
+        </is>
+      </c>
+      <c r="E191" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609291R00307</t>
+        </is>
+      </c>
+      <c r="G191" s="4" t="inlineStr"/>
+      <c r="H191" s="4" t="inlineStr"/>
+    </row>
+    <row r="192" ht="18" customHeight="1">
+      <c r="A192" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="6" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>12:48:26 PM</t>
+        </is>
+      </c>
+      <c r="D192" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609291R00308</t>
+        </is>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609291R00308</t>
+        </is>
+      </c>
+      <c r="G192" s="6" t="inlineStr"/>
+      <c r="H192" s="6" t="inlineStr"/>
+    </row>
+    <row r="193" ht="18" customHeight="1">
+      <c r="A193" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>12:48:33 PM</t>
+        </is>
+      </c>
+      <c r="D193" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609291R00310</t>
+        </is>
+      </c>
+      <c r="E193" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F193" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609291R00310</t>
+        </is>
+      </c>
+      <c r="G193" s="4" t="inlineStr"/>
+      <c r="H193" s="4" t="inlineStr"/>
+    </row>
+    <row r="194" ht="18" customHeight="1">
+      <c r="A194" s="6" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>12:48:42 PM</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609291R00311</t>
+        </is>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609291R00311</t>
+        </is>
+      </c>
+      <c r="G194" s="6" t="inlineStr"/>
+      <c r="H194" s="6" t="inlineStr"/>
+    </row>
+    <row r="195" ht="18" customHeight="1">
+      <c r="A195" s="4" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>12:48:50 PM</t>
+        </is>
+      </c>
+      <c r="D195" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609301R00312</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F195" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609301R00312</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="inlineStr"/>
+      <c r="H195" s="4" t="inlineStr"/>
+    </row>
+    <row r="196" ht="18" customHeight="1">
+      <c r="A196" s="6" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>12:48:58 PM</t>
+        </is>
+      </c>
+      <c r="D196" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609301R00313</t>
+        </is>
+      </c>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609301R00313</t>
+        </is>
+      </c>
+      <c r="G196" s="6" t="inlineStr"/>
+      <c r="H196" s="6" t="inlineStr"/>
+    </row>
+    <row r="197" ht="18" customHeight="1">
+      <c r="A197" s="4" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>12:49:05 PM</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609301R00314</t>
+        </is>
+      </c>
+      <c r="E197" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F197" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609301R00314</t>
+        </is>
+      </c>
+      <c r="G197" s="4" t="inlineStr"/>
+      <c r="H197" s="4" t="inlineStr"/>
+    </row>
+    <row r="198" ht="18" customHeight="1">
+      <c r="A198" s="6" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>12:49:13 PM</t>
+        </is>
+      </c>
+      <c r="D198" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609301R00315</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609301R00315</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr"/>
+      <c r="H198" s="6" t="inlineStr"/>
+    </row>
+    <row r="199" ht="18" customHeight="1">
+      <c r="A199" s="4" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>12:49:21 PM</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609301R00316</t>
+        </is>
+      </c>
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609301R00316</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="inlineStr"/>
+      <c r="H199" s="4" t="inlineStr"/>
+    </row>
+    <row r="200" ht="18" customHeight="1">
+      <c r="A200" s="6" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" s="6" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>12:49:28 PM</t>
+        </is>
+      </c>
+      <c r="D200" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609301R00317</t>
+        </is>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609301R00317</t>
+        </is>
+      </c>
+      <c r="G200" s="6" t="inlineStr"/>
+      <c r="H200" s="6" t="inlineStr"/>
+    </row>
+    <row r="201" ht="18" customHeight="1">
+      <c r="A201" s="4" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>01 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>12:49:37 PM</t>
+        </is>
+      </c>
+      <c r="D201" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610011R00319</t>
+        </is>
+      </c>
+      <c r="E201" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F201" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610011R00319</t>
+        </is>
+      </c>
+      <c r="G201" s="4" t="inlineStr"/>
+      <c r="H201" s="4" t="inlineStr"/>
+    </row>
+    <row r="202" ht="18" customHeight="1">
+      <c r="A202" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" s="6" t="inlineStr">
+        <is>
+          <t>01 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>12:49:45 PM</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202610011R00320</t>
+        </is>
+      </c>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610011R00320</t>
+        </is>
+      </c>
+      <c r="G202" s="6" t="inlineStr"/>
+      <c r="H202" s="6" t="inlineStr"/>
+    </row>
+    <row r="203" ht="18" customHeight="1">
+      <c r="A203" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>03 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>12:50:13 PM</t>
+        </is>
+      </c>
+      <c r="D203" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610031R00321</t>
+        </is>
+      </c>
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F203" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610031R00321</t>
+        </is>
+      </c>
+      <c r="G203" s="4" t="inlineStr"/>
+      <c r="H203" s="4" t="inlineStr"/>
+    </row>
+    <row r="204" ht="18" customHeight="1">
+      <c r="A204" s="6" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" s="6" t="inlineStr">
+        <is>
+          <t>03 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>12:50:20 PM</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202610031R00322</t>
+        </is>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610031R00322</t>
+        </is>
+      </c>
+      <c r="G204" s="6" t="inlineStr"/>
+      <c r="H204" s="6" t="inlineStr"/>
+    </row>
+    <row r="205" ht="18" customHeight="1">
+      <c r="A205" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>03 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>12:50:29 PM</t>
+        </is>
+      </c>
+      <c r="D205" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610031R00323</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F205" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610031R00323</t>
+        </is>
+      </c>
+      <c r="G205" s="4" t="inlineStr"/>
+      <c r="H205" s="4" t="inlineStr"/>
+    </row>
+    <row r="206" ht="18" customHeight="1">
+      <c r="A206" s="6" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" s="6" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>12:50:36 PM</t>
+        </is>
+      </c>
+      <c r="D206" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202610121R00325</t>
+        </is>
+      </c>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610121R00325</t>
+        </is>
+      </c>
+      <c r="G206" s="6" t="inlineStr"/>
+      <c r="H206" s="6" t="inlineStr"/>
+    </row>
+    <row r="207" ht="18" customHeight="1">
+      <c r="A207" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>12:50:46 PM</t>
+        </is>
+      </c>
+      <c r="D207" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610121R00326</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F207" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610121R00326</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="inlineStr"/>
+      <c r="H207" s="4" t="inlineStr"/>
+    </row>
+    <row r="208" ht="18" customHeight="1">
+      <c r="A208" s="6" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>12:50:55 PM</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610161R00332</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610161R00332</t>
+        </is>
+      </c>
+      <c r="G208" s="6" t="inlineStr"/>
+      <c r="H208" s="6" t="inlineStr"/>
+    </row>
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="4" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>12:51:03 PM</t>
+        </is>
+      </c>
+      <c r="D209" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202610161R00334</t>
+        </is>
+      </c>
+      <c r="E209" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610161R00334</t>
+        </is>
+      </c>
+      <c r="G209" s="4" t="inlineStr"/>
+      <c r="H209" s="4" t="inlineStr"/>
+    </row>
+    <row r="210" ht="18" customHeight="1">
+      <c r="A210" s="6" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" s="6" t="inlineStr">
+        <is>
+          <t>25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>12:51:12 PM</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610251R00338</t>
+        </is>
+      </c>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610251R00338</t>
+        </is>
+      </c>
+      <c r="G210" s="6" t="inlineStr"/>
+      <c r="H210" s="6" t="inlineStr"/>
+    </row>
+    <row r="211" ht="18" customHeight="1">
+      <c r="A211" s="4" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>12:51:20 PM</t>
+        </is>
+      </c>
+      <c r="D211" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202610171R00340</t>
+        </is>
+      </c>
+      <c r="E211" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F211" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202610171R00340</t>
+        </is>
+      </c>
+      <c r="G211" s="4" t="inlineStr"/>
+      <c r="H211" s="4" t="inlineStr"/>
+    </row>
+    <row r="212" ht="18" customHeight="1">
+      <c r="A212" s="6" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" s="6" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>12:55:57 PM</t>
+        </is>
+      </c>
+      <c r="D212" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="G212" s="6" t="inlineStr"/>
+      <c r="H212" s="6" t="inlineStr"/>
+    </row>
+    <row r="213" ht="18" customHeight="1">
+      <c r="A213" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>03 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>12:56:07 PM</t>
+        </is>
+      </c>
+      <c r="D213" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202610031R00318</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F213" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202610031R00318</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr"/>
+      <c r="H213" s="4" t="inlineStr"/>
+    </row>
+    <row r="214" ht="18" customHeight="1">
+      <c r="A214" s="6" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>03 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>12:56:15 PM</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202610031R00324</t>
+        </is>
+      </c>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610031R00324</t>
+        </is>
+      </c>
+      <c r="G214" s="6" t="inlineStr"/>
+      <c r="H214" s="6" t="inlineStr"/>
+    </row>
+    <row r="215" ht="18" customHeight="1">
+      <c r="A215" s="4" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>03 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>12:57:10 PM</t>
+        </is>
+      </c>
+      <c r="D215" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202610031R00318</t>
+        </is>
+      </c>
+      <c r="E215" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F215" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202610031R00318</t>
+        </is>
+      </c>
+      <c r="G215" s="4" t="inlineStr"/>
+      <c r="H215" s="4" t="inlineStr"/>
+    </row>
+    <row r="216" ht="18" customHeight="1">
+      <c r="A216" s="6" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" s="6" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>12:58:23 PM</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr"/>
+      <c r="H216" s="6" t="inlineStr"/>
+    </row>
+    <row r="217" ht="18" customHeight="1">
+      <c r="A217" s="4" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>12:58:39 PM</t>
+        </is>
+      </c>
+      <c r="D217" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202610121R00327</t>
+        </is>
+      </c>
+      <c r="E217" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F217" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202610121R00327</t>
+        </is>
+      </c>
+      <c r="G217" s="4" t="inlineStr"/>
+      <c r="H217" s="4" t="inlineStr"/>
+    </row>
+    <row r="218" ht="18" customHeight="1">
+      <c r="A218" s="6" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" s="6" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>12:58:46 PM</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610121R00328</t>
+        </is>
+      </c>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610121R00328</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr"/>
+      <c r="H218" s="6" t="inlineStr"/>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="4" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>12 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>12:58:54 PM</t>
+        </is>
+      </c>
+      <c r="D219" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202610121R00329</t>
+        </is>
+      </c>
+      <c r="E219" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610121R00329</t>
+        </is>
+      </c>
+      <c r="G219" s="4" t="inlineStr"/>
+      <c r="H219" s="4" t="inlineStr"/>
+    </row>
+    <row r="220" ht="18" customHeight="1">
+      <c r="A220" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" s="6" t="inlineStr">
+        <is>
+          <t>16 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>12:59:01 PM</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610161R00333</t>
+        </is>
+      </c>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610161R00333</t>
+        </is>
+      </c>
+      <c r="G220" s="6" t="inlineStr"/>
+      <c r="H220" s="6" t="inlineStr"/>
+    </row>
+    <row r="221" ht="18" customHeight="1">
+      <c r="A221" s="4" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>12:59:09 PM</t>
+        </is>
+      </c>
+      <c r="D221" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202610171R00336</t>
+        </is>
+      </c>
+      <c r="E221" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F221" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610171R00336</t>
+        </is>
+      </c>
+      <c r="G221" s="4" t="inlineStr"/>
+      <c r="H221" s="4" t="inlineStr"/>
+    </row>
+    <row r="222" ht="18" customHeight="1">
+      <c r="A222" s="6" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>17 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>12:59:17 PM</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="inlineStr">
+        <is>
+          <t>ABA61202610171R00337</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610171R00337</t>
+        </is>
+      </c>
+      <c r="G222" s="6" t="inlineStr"/>
+      <c r="H222" s="6" t="inlineStr"/>
+    </row>
+    <row r="223" ht="18" customHeight="1">
+      <c r="A223" s="4" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>25 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>12:59:24 PM</t>
+        </is>
+      </c>
+      <c r="D223" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202610251R00339</t>
+        </is>
+      </c>
+      <c r="E223" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F223" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202610251R00339</t>
+        </is>
+      </c>
+      <c r="G223" s="4" t="inlineStr"/>
+      <c r="H223" s="4" t="inlineStr"/>
+    </row>
+    <row r="224" ht="18" customHeight="1">
+      <c r="A224" s="6" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" s="6" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>02:44:52 PM</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="G224" s="6" t="inlineStr"/>
+      <c r="H224" s="6" t="inlineStr"/>
+    </row>
+    <row r="225" ht="18" customHeight="1">
+      <c r="A225" s="4" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>02:45:02 PM</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="E225" s="4" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F225" s="5" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609291R00309</t>
+        </is>
+      </c>
+      <c r="G225" s="4" t="inlineStr"/>
+      <c r="H225" s="4" t="inlineStr"/>
+    </row>
+    <row r="226" ht="18" customHeight="1">
+      <c r="A226" s="6" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>29 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>02:45:43 PM</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="inlineStr">
+        <is>
+          <t>ABA41202609292R00309</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>16P</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>VQ150010:ABA41202609292R00309</t>
+        </is>
+      </c>
+      <c r="G226" s="6" t="inlineStr"/>
+      <c r="H226" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H226"/>
+  <dimension ref="A1:H230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7671,6 +7671,134 @@
       <c r="G226" s="6" t="inlineStr"/>
       <c r="H226" s="6" t="inlineStr"/>
     </row>
+    <row r="227" ht="18" customHeight="1">
+      <c r="A227" s="4" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>16 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>03:25:50 PM</t>
+        </is>
+      </c>
+      <c r="D227" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="E227" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F227" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="G227" s="4" t="inlineStr"/>
+      <c r="H227" s="4" t="inlineStr"/>
+    </row>
+    <row r="228" ht="18" customHeight="1">
+      <c r="A228" s="6" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" s="6" t="inlineStr">
+        <is>
+          <t>16 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>03:26:49 PM</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="G228" s="6" t="inlineStr"/>
+      <c r="H228" s="6" t="inlineStr"/>
+    </row>
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="4" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>16 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>03:27:48 PM</t>
+        </is>
+      </c>
+      <c r="D229" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="E229" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="G229" s="4" t="inlineStr"/>
+      <c r="H229" s="4" t="inlineStr"/>
+    </row>
+    <row r="230" ht="18" customHeight="1">
+      <c r="A230" s="6" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" s="6" t="inlineStr">
+        <is>
+          <t>16 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>03:28:33 PM</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202609162S00279</t>
+        </is>
+      </c>
+      <c r="G230" s="6" t="inlineStr"/>
+      <c r="H230" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H230"/>
+  <dimension ref="A1:H233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7799,6 +7799,102 @@
       <c r="G230" s="6" t="inlineStr"/>
       <c r="H230" s="6" t="inlineStr"/>
     </row>
+    <row r="231" ht="18" customHeight="1">
+      <c r="A231" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>04:18:22 PM</t>
+        </is>
+      </c>
+      <c r="D231" s="5" t="inlineStr">
+        <is>
+          <t>ABS11202610291U00002</t>
+        </is>
+      </c>
+      <c r="E231" s="4" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F231" s="5" t="inlineStr">
+        <is>
+          <t>VX155810:ABS11202610291U00002</t>
+        </is>
+      </c>
+      <c r="G231" s="4" t="inlineStr"/>
+      <c r="H231" s="4" t="inlineStr"/>
+    </row>
+    <row r="232" ht="18" customHeight="1">
+      <c r="A232" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" s="6" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>04:29:26 PM</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>ABS11202610291U00002</t>
+        </is>
+      </c>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>VX155810:ABS11202610291U00002</t>
+        </is>
+      </c>
+      <c r="G232" s="6" t="inlineStr"/>
+      <c r="H232" s="6" t="inlineStr"/>
+    </row>
+    <row r="233" ht="18" customHeight="1">
+      <c r="A233" s="4" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>04:30:56 PM</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>ABS11202610291U00002</t>
+        </is>
+      </c>
+      <c r="E233" s="4" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F233" s="5" t="inlineStr">
+        <is>
+          <t>VX155810:ABS11202610291U00002</t>
+        </is>
+      </c>
+      <c r="G233" s="4" t="inlineStr"/>
+      <c r="H233" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3036" yWindow="2340" windowWidth="11268" windowHeight="9900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H233"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -7895,6 +7895,230 @@
       <c r="G233" s="4" t="inlineStr"/>
       <c r="H233" s="4" t="inlineStr"/>
     </row>
+    <row r="234" ht="18" customHeight="1">
+      <c r="A234" s="6" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" s="6" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>09:07:11 PM</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="inlineStr">
+        <is>
+          <t>ABS11202610291R00108</t>
+        </is>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>BP00000129:ABS11202610291R00108</t>
+        </is>
+      </c>
+      <c r="G234" s="6" t="inlineStr"/>
+      <c r="H234" s="6" t="inlineStr"/>
+    </row>
+    <row r="235" ht="18" customHeight="1">
+      <c r="A235" s="4" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>09:17:24 PM</t>
+        </is>
+      </c>
+      <c r="D235" s="5" t="inlineStr">
+        <is>
+          <t>ACS11202610291R00001</t>
+        </is>
+      </c>
+      <c r="E235" s="4" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610291R00001</t>
+        </is>
+      </c>
+      <c r="G235" s="4" t="inlineStr"/>
+      <c r="H235" s="4" t="inlineStr"/>
+    </row>
+    <row r="236" ht="18" customHeight="1">
+      <c r="A236" s="6" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" s="6" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>10:05:58 PM</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>ACS11202610291U00010</t>
+        </is>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610291U00010</t>
+        </is>
+      </c>
+      <c r="G236" s="6" t="inlineStr"/>
+      <c r="H236" s="6" t="inlineStr"/>
+    </row>
+    <row r="237" ht="18" customHeight="1">
+      <c r="A237" s="4" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>10:07:35 PM</t>
+        </is>
+      </c>
+      <c r="D237" s="5" t="inlineStr">
+        <is>
+          <t>ACS11202610292U00010</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F237" s="5" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610292U00010</t>
+        </is>
+      </c>
+      <c r="G237" s="4" t="inlineStr"/>
+      <c r="H237" s="4" t="inlineStr"/>
+    </row>
+    <row r="238" ht="18" customHeight="1">
+      <c r="A238" s="6" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" s="6" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>10:12:44 PM</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>ACS11202610291U00011</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610291U00011</t>
+        </is>
+      </c>
+      <c r="G238" s="6" t="inlineStr"/>
+      <c r="H238" s="6" t="inlineStr"/>
+    </row>
+    <row r="239" ht="18" customHeight="1">
+      <c r="A239" s="4" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>10:15:45 PM</t>
+        </is>
+      </c>
+      <c r="D239" s="5" t="inlineStr">
+        <is>
+          <t>ACS11202610291U00012</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610291U00012</t>
+        </is>
+      </c>
+      <c r="G239" s="4" t="inlineStr"/>
+      <c r="H239" s="4" t="inlineStr"/>
+    </row>
+    <row r="240" ht="18" customHeight="1">
+      <c r="A240" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" s="6" t="inlineStr">
+        <is>
+          <t>29 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>10:16:49 PM</t>
+        </is>
+      </c>
+      <c r="D240" s="7" t="inlineStr">
+        <is>
+          <t>ACS11202610291U00015</t>
+        </is>
+      </c>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610291U00015</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr"/>
+      <c r="H240" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3036" yWindow="2340" windowWidth="11268" windowHeight="9900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pack ID" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H240"/>
+  <dimension ref="A1:H250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8119,6 +8119,326 @@
       <c r="G240" s="6" t="inlineStr"/>
       <c r="H240" s="6" t="inlineStr"/>
     </row>
+    <row r="241" ht="18" customHeight="1">
+      <c r="A241" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>09:21:04 AM</t>
+        </is>
+      </c>
+      <c r="D241" s="5" t="inlineStr">
+        <is>
+          <t>ACS21202610301R00001</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>SW_RH_8P</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS21202610301R00001</t>
+        </is>
+      </c>
+      <c r="G241" s="4" t="inlineStr"/>
+      <c r="H241" s="4" t="inlineStr"/>
+    </row>
+    <row r="242" ht="18" customHeight="1">
+      <c r="A242" s="6" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" s="6" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>09:21:12 AM</t>
+        </is>
+      </c>
+      <c r="D242" s="7" t="inlineStr">
+        <is>
+          <t>ACS11202610301R00001</t>
+        </is>
+      </c>
+      <c r="E242" s="6" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610301R00001</t>
+        </is>
+      </c>
+      <c r="G242" s="6" t="inlineStr"/>
+      <c r="H242" s="6" t="inlineStr"/>
+    </row>
+    <row r="243" ht="18" customHeight="1">
+      <c r="A243" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>15 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>09:21:53 AM</t>
+        </is>
+      </c>
+      <c r="D243" s="5" t="inlineStr">
+        <is>
+          <t>ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>27P</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="inlineStr">
+        <is>
+          <t>VQ150030:ABA61202609151R00276</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="inlineStr"/>
+      <c r="H243" s="4" t="inlineStr"/>
+    </row>
+    <row r="244" ht="18" customHeight="1">
+      <c r="A244" s="6" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" s="6" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>09:26:48 AM</t>
+        </is>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="G244" s="6" t="inlineStr"/>
+      <c r="H244" s="6" t="inlineStr"/>
+    </row>
+    <row r="245" ht="18" customHeight="1">
+      <c r="A245" s="4" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>24 Sep 2026</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>09:27:54 AM</t>
+        </is>
+      </c>
+      <c r="D245" s="5" t="inlineStr">
+        <is>
+          <t>ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>12P</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="inlineStr">
+        <is>
+          <t>VQ150000:ABA31202609241R00295</t>
+        </is>
+      </c>
+      <c r="G245" s="4" t="inlineStr"/>
+      <c r="H245" s="4" t="inlineStr"/>
+    </row>
+    <row r="246" ht="18" customHeight="1">
+      <c r="A246" s="6" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" s="6" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>09:31:36 AM</t>
+        </is>
+      </c>
+      <c r="D246" s="7" t="inlineStr">
+        <is>
+          <t>ACS31202610301R00002</t>
+        </is>
+      </c>
+      <c r="E246" s="6" t="inlineStr">
+        <is>
+          <t>SW_LH_10P</t>
+        </is>
+      </c>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>BP00000002:ACS31202610301R00002</t>
+        </is>
+      </c>
+      <c r="G246" s="6" t="inlineStr"/>
+      <c r="H246" s="6" t="inlineStr"/>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="A247" s="4" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>10:22:49 AM</t>
+        </is>
+      </c>
+      <c r="D247" s="5" t="inlineStr">
+        <is>
+          <t>ABA51202610301U00005</t>
+        </is>
+      </c>
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>VX156060:ABA51202610301U00005</t>
+        </is>
+      </c>
+      <c r="G247" s="4" t="inlineStr"/>
+      <c r="H247" s="4" t="inlineStr"/>
+    </row>
+    <row r="248" ht="18" customHeight="1">
+      <c r="A248" s="6" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" s="6" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>10:22:54 AM</t>
+        </is>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>ABA51202610301R00006</t>
+        </is>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>24P</t>
+        </is>
+      </c>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>VQ150020:ABA51202610301R00006</t>
+        </is>
+      </c>
+      <c r="G248" s="6" t="inlineStr"/>
+      <c r="H248" s="6" t="inlineStr"/>
+    </row>
+    <row r="249" ht="18" customHeight="1">
+      <c r="A249" s="4" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>10:22:59 AM</t>
+        </is>
+      </c>
+      <c r="D249" s="5" t="inlineStr">
+        <is>
+          <t>ACS11202610301R00007</t>
+        </is>
+      </c>
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>SW_LH_8P</t>
+        </is>
+      </c>
+      <c r="F249" s="5" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS11202610301R00007</t>
+        </is>
+      </c>
+      <c r="G249" s="4" t="inlineStr"/>
+      <c r="H249" s="4" t="inlineStr"/>
+    </row>
+    <row r="250" ht="18" customHeight="1">
+      <c r="A250" s="6" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" s="6" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>10:23:04 AM</t>
+        </is>
+      </c>
+      <c r="D250" s="7" t="inlineStr">
+        <is>
+          <t>ADT11202610301R00008</t>
+        </is>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>TS_8P</t>
+        </is>
+      </c>
+      <c r="F250" s="7" t="inlineStr">
+        <is>
+          <t>BP00000131:ADT11202610301R00008</t>
+        </is>
+      </c>
+      <c r="G250" s="6" t="inlineStr"/>
+      <c r="H250" s="6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/models/hv/data/pack_id_scan_log.xlsx
+++ b/models/hv/data/pack_id_scan_log.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H250"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -8439,6 +8439,86 @@
       <c r="G250" s="6" t="inlineStr"/>
       <c r="H250" s="6" t="inlineStr"/>
     </row>
+    <row r="251" ht="18" customHeight="1">
+      <c r="A251" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>12:29:56 PM</t>
+        </is>
+      </c>
+      <c r="D251" s="5" t="inlineStr">
+        <is>
+          <t>ACS21202610301R00001</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>SW_RH_8P</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="inlineStr">
+        <is>
+          <t>BP00000129:ACS21202610301R00001</t>
+        </is>
+      </c>
+      <c r="G251" s="4" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="18" customHeight="1">
+      <c r="A252" s="6" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" s="6" t="inlineStr">
+        <is>
+          <t>30 Oct 2026</t>
+        </is>
+      </c>
+      <c r="C252" s="6" t="inlineStr">
+        <is>
+          <t>12:30:14 PM</t>
+        </is>
+      </c>
+      <c r="D252" s="7" t="inlineStr">
+        <is>
+          <t>ADT11202610301R00006</t>
+        </is>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>TS_8P</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>BP00000131:ADT11202610301R00006</t>
+        </is>
+      </c>
+      <c r="G252" s="6" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="H252" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
